--- a/exports/preview_campana_baja_precio_ola1_20260520.xlsx
+++ b/exports/preview_campana_baja_precio_ola1_20260520.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S462"/>
+  <dimension ref="A1:S463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>125.19%</t>
+          <t>124.63%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3967.85</v>
+        <v>3957.95</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
@@ -797,7 +797,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82.69%</t>
+          <t>78.98%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4166.25</v>
+        <v>4081.63</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8.68</v>
+        <v>8.66</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8927.67</v>
+        <v>8905.379999999999</v>
       </c>
       <c r="M7" t="n">
         <v>88</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-7.63%</t>
+          <t>-7.86%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4215.85</v>
+        <v>4205.32</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24.23%</t>
+          <t>23.92%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1339.15</v>
+        <v>1335.81</v>
       </c>
       <c r="M10" t="n">
         <v>22</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-74.84%</t>
+          <t>-74.90%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>17.36</v>
+        <v>17.32</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1859.93</v>
+        <v>1855.29</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23.20%</t>
+          <t>22.90%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1735.94</v>
+        <v>1731.6</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1611.94</v>
+        <v>1607.92</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.99%</t>
+          <t>22.68%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2355.91</v>
+        <v>2350.03</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3558.67</v>
+        <v>3549.78</v>
       </c>
       <c r="M19" t="n">
         <v>22</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7439.73</v>
+        <v>7421.15</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1239.95</v>
+        <v>1236.86</v>
       </c>
       <c r="M21" t="n">
         <v>88</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1983.93</v>
+        <v>1978.97</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4250</v>
+        <v>4140</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2975.89</v>
+        <v>2968.46</v>
       </c>
       <c r="M25" t="n">
         <v>22</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-16.88%</t>
+          <t>-17.09%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1135.8</v>
+        <v>1132.96</v>
       </c>
       <c r="M30" t="n">
         <v>100</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>967.16</v>
+        <v>964.75</v>
       </c>
       <c r="M31" t="n">
         <v>66</v>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3099.89</v>
+        <v>3092.15</v>
       </c>
       <c r="M32" t="n">
         <v>100</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-4.21%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>6695.75</v>
+        <v>6679.04</v>
       </c>
       <c r="M51" t="n">
         <v>100</v>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>7.61%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1559.86</v>
+        <v>1555.97</v>
       </c>
       <c r="M53" t="n">
         <v>100</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>-87.42%</t>
+          <t>-87.45%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>8.68</v>
+        <v>8.66</v>
       </c>
       <c r="M56" t="n">
         <v>100</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1983.93</v>
+        <v>1978.97</v>
       </c>
       <c r="M70" t="n">
         <v>88</v>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>95.76%</t>
+          <t>95.27%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2727.9</v>
+        <v>2721.09</v>
       </c>
       <c r="M72" t="n">
         <v>100</v>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>415.67%</t>
+          <t>414.38%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>5455.8</v>
+        <v>5442.18</v>
       </c>
       <c r="M76" t="n">
         <v>100</v>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4463.84</v>
+        <v>4452.69</v>
       </c>
       <c r="M80" t="n">
         <v>88</v>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>-22.54%</t>
+          <t>-22.73%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2628.7</v>
+        <v>2622.14</v>
       </c>
       <c r="M84" t="n">
         <v>100</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>6323.77</v>
+        <v>6307.98</v>
       </c>
       <c r="M86" t="n">
         <v>88</v>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>-33.46%</t>
+          <t>-33.63%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>27.28</v>
+        <v>27.21</v>
       </c>
       <c r="M91" t="n">
         <v>100</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>-19.40%</t>
+          <t>-19.60%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>32.24</v>
+        <v>32.16</v>
       </c>
       <c r="M95" t="n">
         <v>100</v>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3719.86</v>
+        <v>3710.58</v>
       </c>
       <c r="M96" t="n">
         <v>100</v>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2107.92</v>
+        <v>2102.66</v>
       </c>
       <c r="M99" t="n">
         <v>88</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1016.76</v>
+        <v>1014.22</v>
       </c>
       <c r="M101" t="n">
         <v>100</v>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>5.03%</t>
+          <t>4.77%</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -9854,7 +9854,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2231.92</v>
+        <v>2226.35</v>
       </c>
       <c r="M108" t="n">
         <v>100</v>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>415.67%</t>
+          <t>414.38%</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -10119,7 +10119,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>5455.8</v>
+        <v>5442.18</v>
       </c>
       <c r="M111" t="n">
         <v>100</v>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>129.38%</t>
+          <t>128.81%</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -10558,7 +10558,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>4339.84</v>
+        <v>4329.01</v>
       </c>
       <c r="M116" t="n">
         <v>100</v>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>158.75%</t>
+          <t>158.10%</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -11167,7 +11167,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>15871.42</v>
+        <v>15831.79</v>
       </c>
       <c r="M123" t="n">
         <v>22</v>
@@ -11258,7 +11258,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1729.74</v>
+        <v>1725.42</v>
       </c>
       <c r="M124" t="n">
         <v>100</v>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>-16.35%</t>
+          <t>-16.56%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1785.53</v>
+        <v>1781.08</v>
       </c>
       <c r="M131" t="n">
         <v>100</v>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>-21.84%</t>
+          <t>-22.04%</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2430.31</v>
+        <v>2424.24</v>
       </c>
       <c r="M133" t="n">
         <v>100</v>
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>33.96%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>10415.62</v>
+        <v>10389.61</v>
       </c>
       <c r="M137" t="n">
         <v>100</v>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1363.95</v>
+        <v>1360.54</v>
       </c>
       <c r="M139" t="n">
         <v>100</v>
@@ -14141,7 +14141,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2727.9</v>
+        <v>2721.09</v>
       </c>
       <c r="M157" t="n">
         <v>100</v>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>26.45%</t>
+          <t>26.13%</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -14576,7 +14576,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>3967.85</v>
+        <v>3957.95</v>
       </c>
       <c r="M162" t="n">
         <v>100</v>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -14750,7 +14750,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>21079.23</v>
+        <v>21026.6</v>
       </c>
       <c r="M164" t="n">
         <v>88</v>
@@ -14932,7 +14932,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1983.93</v>
+        <v>1978.97</v>
       </c>
       <c r="M166" t="n">
         <v>66</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>39678.54</v>
+        <v>39579.48</v>
       </c>
       <c r="M171" t="n">
         <v>100</v>
@@ -15462,7 +15462,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>619.98</v>
+        <v>618.4299999999999</v>
       </c>
       <c r="M172" t="n">
         <v>66</v>
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>3695.06</v>
+        <v>3685.84</v>
       </c>
       <c r="M179" t="n">
         <v>22</v>
@@ -16170,7 +16170,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>4935.02</v>
+        <v>4922.7</v>
       </c>
       <c r="M180" t="n">
         <v>22</v>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>12.98%</t>
+          <t>12.70%</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -16261,7 +16261,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1735.94</v>
+        <v>1731.6</v>
       </c>
       <c r="M181" t="n">
         <v>100</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>-10.93%</t>
+          <t>-11.16%</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2851.9</v>
+        <v>2844.77</v>
       </c>
       <c r="M182" t="n">
         <v>100</v>
@@ -16609,7 +16609,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2851.9</v>
+        <v>2844.77</v>
       </c>
       <c r="M185" t="n">
         <v>22</v>
@@ -16787,7 +16787,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>1487.95</v>
+        <v>1484.23</v>
       </c>
       <c r="M187" t="n">
         <v>22</v>
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>1686.34</v>
+        <v>1682.13</v>
       </c>
       <c r="M190" t="n">
         <v>22</v>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -17321,7 +17321,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2990</v>
+        <v>2890</v>
       </c>
       <c r="M193" t="n">
         <v>100</v>
@@ -18199,7 +18199,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>3099.89</v>
+        <v>3092.15</v>
       </c>
       <c r="M203" t="n">
         <v>22</v>
@@ -18377,7 +18377,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2727.9</v>
+        <v>2721.09</v>
       </c>
       <c r="M205" t="n">
         <v>22</v>
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>890.29</v>
+        <v>888.0599999999999</v>
       </c>
       <c r="M210" t="n">
         <v>22</v>
@@ -18966,7 +18966,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>61.72%</t>
+          <t>61.32%</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -18998,7 +18998,7 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>3967.85</v>
+        <v>3957.95</v>
       </c>
       <c r="M212" t="n">
         <v>100</v>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>37.53%</t>
+          <t>37.19%</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>4711.83</v>
+        <v>4700.06</v>
       </c>
       <c r="M218" t="n">
         <v>100</v>
@@ -19702,7 +19702,7 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>7439.73</v>
+        <v>7421.15</v>
       </c>
       <c r="M220" t="n">
         <v>22</v>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>72.01%</t>
+          <t>71.58%</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -20058,7 +20058,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>4215.85</v>
+        <v>4205.32</v>
       </c>
       <c r="M224" t="n">
         <v>100</v>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>172.87%</t>
+          <t>172.19%</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -20236,7 +20236,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>5207.81</v>
+        <v>5194.81</v>
       </c>
       <c r="M226" t="n">
         <v>100</v>
@@ -20469,7 +20469,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>100.28%</t>
+          <t>99.78%</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -20501,7 +20501,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>4959.82</v>
+        <v>4947.43</v>
       </c>
       <c r="M229" t="n">
         <v>100</v>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>285.97%</t>
+          <t>285.01%</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -20762,7 +20762,7 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>3558.67</v>
+        <v>3549.78</v>
       </c>
       <c r="M232" t="n">
         <v>100</v>
@@ -20817,7 +20817,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>41.61%</t>
+          <t>41.25%</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -20849,7 +20849,7 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>1983.93</v>
+        <v>1978.97</v>
       </c>
       <c r="M233" t="n">
         <v>22</v>
@@ -21118,7 +21118,7 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>1363.95</v>
+        <v>1360.54</v>
       </c>
       <c r="M236" t="n">
         <v>22</v>
@@ -21300,7 +21300,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>3967.85</v>
+        <v>3957.95</v>
       </c>
       <c r="M238" t="n">
         <v>100</v>
@@ -21474,7 +21474,7 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>3719.86</v>
+        <v>3710.58</v>
       </c>
       <c r="M240" t="n">
         <v>88</v>
@@ -21565,7 +21565,7 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>3943.06</v>
+        <v>3933.21</v>
       </c>
       <c r="M241" t="n">
         <v>22</v>
@@ -21743,7 +21743,7 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>1859.93</v>
+        <v>1855.29</v>
       </c>
       <c r="M243" t="n">
         <v>22</v>
@@ -22273,7 +22273,7 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>9175.66</v>
+        <v>9152.75</v>
       </c>
       <c r="M249" t="n">
         <v>100</v>
@@ -22360,7 +22360,7 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>1487.95</v>
+        <v>1484.23</v>
       </c>
       <c r="M250" t="n">
         <v>22</v>
@@ -22419,7 +22419,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>158.81%</t>
+          <t>158.16%</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -22451,7 +22451,7 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>15871.42</v>
+        <v>15831.79</v>
       </c>
       <c r="M251" t="n">
         <v>22</v>
@@ -22542,7 +22542,7 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>13813.09</v>
+        <v>13778.61</v>
       </c>
       <c r="M252" t="n">
         <v>100</v>
@@ -22629,7 +22629,7 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>12399.55</v>
+        <v>12368.59</v>
       </c>
       <c r="M253" t="n">
         <v>22</v>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>145.29%</t>
+          <t>144.67%</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -23602,7 +23602,7 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>8431.690000000001</v>
+        <v>8410.639999999999</v>
       </c>
       <c r="M264" t="n">
         <v>100</v>
@@ -23780,7 +23780,7 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>1339.15</v>
+        <v>1335.81</v>
       </c>
       <c r="M266" t="n">
         <v>100</v>
@@ -24444,7 +24444,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>36.20%</t>
+          <t>35.86%</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -24476,7 +24476,7 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2628.7</v>
+        <v>2622.14</v>
       </c>
       <c r="M274" t="n">
         <v>100</v>
@@ -24618,7 +24618,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>217.94%</t>
+          <t>217.14%</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -24650,7 +24650,7 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>2975.89</v>
+        <v>2968.46</v>
       </c>
       <c r="M276" t="n">
         <v>100</v>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>14.07%</t>
+          <t>13.78%</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>5455.8</v>
+        <v>5442.18</v>
       </c>
       <c r="M278" t="n">
         <v>100</v>
@@ -25053,7 +25053,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>36.08%</t>
+          <t>35.74%</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -25085,7 +25085,7 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>4215.85</v>
+        <v>4205.32</v>
       </c>
       <c r="M281" t="n">
         <v>100</v>
@@ -25227,7 +25227,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>58.13%</t>
+          <t>57.74%</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -25259,7 +25259,7 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>4959.82</v>
+        <v>4947.43</v>
       </c>
       <c r="M283" t="n">
         <v>100</v>
@@ -25346,7 +25346,7 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2430.31</v>
+        <v>2424.24</v>
       </c>
       <c r="M284" t="n">
         <v>88</v>
@@ -25437,7 +25437,7 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>669.58</v>
+        <v>667.9</v>
       </c>
       <c r="M285" t="n">
         <v>22</v>
@@ -25702,7 +25702,7 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>3843.86</v>
+        <v>3834.26</v>
       </c>
       <c r="M288" t="n">
         <v>88</v>
@@ -25793,7 +25793,7 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>619.98</v>
+        <v>618.4299999999999</v>
       </c>
       <c r="M289" t="n">
         <v>22</v>
@@ -25852,7 +25852,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>38.80%</t>
+          <t>38.45%</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>8481.290000000001</v>
+        <v>8460.110000000001</v>
       </c>
       <c r="M290" t="n">
         <v>100</v>
@@ -26058,7 +26058,7 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>2107.92</v>
+        <v>2102.66</v>
       </c>
       <c r="M292" t="n">
         <v>88</v>
@@ -26117,7 +26117,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>160.08%</t>
+          <t>159.43%</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -26149,7 +26149,7 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>7067.74</v>
+        <v>7050.09</v>
       </c>
       <c r="M293" t="n">
         <v>100</v>
@@ -26204,7 +26204,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>-14.85%</t>
+          <t>-15.06%</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -26236,7 +26236,7 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>1611.94</v>
+        <v>1607.92</v>
       </c>
       <c r="M294" t="n">
         <v>100</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>28.45%</t>
+          <t>28.13%</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -26410,7 +26410,7 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>1983.93</v>
+        <v>1978.97</v>
       </c>
       <c r="M296" t="n">
         <v>100</v>
@@ -26584,7 +26584,7 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>5604.59</v>
+        <v>5590.6</v>
       </c>
       <c r="M298" t="n">
         <v>100</v>
@@ -26758,7 +26758,7 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>3099.89</v>
+        <v>3092.15</v>
       </c>
       <c r="M300" t="n">
         <v>88</v>
@@ -27023,7 +27023,7 @@
         </is>
       </c>
       <c r="L303" t="n">
-        <v>2405.51</v>
+        <v>2399.51</v>
       </c>
       <c r="M303" t="n">
         <v>22</v>
@@ -27114,7 +27114,7 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>1041.56</v>
+        <v>1038.96</v>
       </c>
       <c r="M304" t="n">
         <v>88</v>
@@ -27205,7 +27205,7 @@
         </is>
       </c>
       <c r="L305" t="n">
-        <v>507.39</v>
+        <v>506.12</v>
       </c>
       <c r="M305" t="n">
         <v>88</v>
@@ -27296,7 +27296,7 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>1614.42</v>
+        <v>1610.39</v>
       </c>
       <c r="M306" t="n">
         <v>88</v>
@@ -27387,7 +27387,7 @@
         </is>
       </c>
       <c r="L307" t="n">
-        <v>619.98</v>
+        <v>618.4299999999999</v>
       </c>
       <c r="M307" t="n">
         <v>22</v>
@@ -27533,7 +27533,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>59.61%</t>
+          <t>59.21%</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -27565,7 +27565,7 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>4339.84</v>
+        <v>4329.01</v>
       </c>
       <c r="M309" t="n">
         <v>100</v>
@@ -28008,7 +28008,7 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>3719.86</v>
+        <v>3710.58</v>
       </c>
       <c r="M314" t="n">
         <v>22</v>
@@ -28099,7 +28099,7 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>3447.07</v>
+        <v>3438.47</v>
       </c>
       <c r="M315" t="n">
         <v>22</v>
@@ -28190,7 +28190,7 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>6199.77</v>
+        <v>6184.29</v>
       </c>
       <c r="M316" t="n">
         <v>22</v>
@@ -28281,7 +28281,7 @@
         </is>
       </c>
       <c r="L317" t="n">
-        <v>3543.38</v>
+        <v>3534.53</v>
       </c>
       <c r="M317" t="n">
         <v>22</v>
@@ -28641,7 +28641,7 @@
         </is>
       </c>
       <c r="L321" t="n">
-        <v>1239.95</v>
+        <v>1236.86</v>
       </c>
       <c r="M321" t="n">
         <v>22</v>
@@ -28732,7 +28732,7 @@
         </is>
       </c>
       <c r="L322" t="n">
-        <v>4513.43</v>
+        <v>4502.17</v>
       </c>
       <c r="M322" t="n">
         <v>100</v>
@@ -29001,7 +29001,7 @@
         </is>
       </c>
       <c r="L325" t="n">
-        <v>7067.74</v>
+        <v>7050.09</v>
       </c>
       <c r="M325" t="n">
         <v>100</v>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>113.47%</t>
+          <t>112.93%</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -29088,7 +29088,7 @@
         </is>
       </c>
       <c r="L326" t="n">
-        <v>3595.87</v>
+        <v>3586.89</v>
       </c>
       <c r="M326" t="n">
         <v>100</v>
@@ -29175,7 +29175,7 @@
         </is>
       </c>
       <c r="L327" t="n">
-        <v>1983.93</v>
+        <v>1978.97</v>
       </c>
       <c r="M327" t="n">
         <v>100</v>
@@ -29408,7 +29408,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>73.06%</t>
+          <t>72.62%</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -29440,7 +29440,7 @@
         </is>
       </c>
       <c r="L330" t="n">
-        <v>6199.77</v>
+        <v>6184.29</v>
       </c>
       <c r="M330" t="n">
         <v>88</v>
@@ -29622,7 +29622,7 @@
         </is>
       </c>
       <c r="L332" t="n">
-        <v>7935.71</v>
+        <v>7915.9</v>
       </c>
       <c r="M332" t="n">
         <v>0</v>
@@ -29671,7 +29671,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -29713,7 +29713,7 @@
         </is>
       </c>
       <c r="L333" t="n">
-        <v>45446.81</v>
+        <v>45333.34</v>
       </c>
       <c r="M333" t="n">
         <v>22</v>
@@ -29891,7 +29891,7 @@
         </is>
       </c>
       <c r="L335" t="n">
-        <v>3223.88</v>
+        <v>3215.83</v>
       </c>
       <c r="M335" t="n">
         <v>66</v>
@@ -30164,7 +30164,7 @@
         </is>
       </c>
       <c r="L338" t="n">
-        <v>1487.95</v>
+        <v>1484.23</v>
       </c>
       <c r="M338" t="n">
         <v>88</v>
@@ -30223,7 +30223,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>556.85%</t>
+          <t>555.21%</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -30255,7 +30255,7 @@
         </is>
       </c>
       <c r="L339" t="n">
-        <v>13639.5</v>
+        <v>13605.45</v>
       </c>
       <c r="M339" t="n">
         <v>22</v>
@@ -30433,7 +30433,7 @@
         </is>
       </c>
       <c r="L341" t="n">
-        <v>6199.77</v>
+        <v>6184.29</v>
       </c>
       <c r="M341" t="n">
         <v>22</v>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>292.78%</t>
+          <t>291.80%</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -30698,7 +30698,7 @@
         </is>
       </c>
       <c r="L344" t="n">
-        <v>23559.14</v>
+        <v>23500.32</v>
       </c>
       <c r="M344" t="n">
         <v>88</v>
@@ -31050,7 +31050,7 @@
         </is>
       </c>
       <c r="L348" t="n">
-        <v>4215.85</v>
+        <v>4205.32</v>
       </c>
       <c r="M348" t="n">
         <v>88</v>
@@ -31837,7 +31837,7 @@
         </is>
       </c>
       <c r="L357" t="n">
-        <v>7067.74</v>
+        <v>7050.09</v>
       </c>
       <c r="M357" t="n">
         <v>100</v>
@@ -31924,7 +31924,7 @@
         </is>
       </c>
       <c r="L358" t="n">
-        <v>3471.87</v>
+        <v>3463.2</v>
       </c>
       <c r="M358" t="n">
         <v>100</v>
@@ -32011,7 +32011,7 @@
         </is>
       </c>
       <c r="L359" t="n">
-        <v>1487.95</v>
+        <v>1484.23</v>
       </c>
       <c r="M359" t="n">
         <v>100</v>
@@ -32098,7 +32098,7 @@
         </is>
       </c>
       <c r="L360" t="n">
-        <v>3223.88</v>
+        <v>3215.83</v>
       </c>
       <c r="M360" t="n">
         <v>0</v>
@@ -32189,7 +32189,7 @@
         </is>
       </c>
       <c r="L361" t="n">
-        <v>3719.86</v>
+        <v>3710.58</v>
       </c>
       <c r="M361" t="n">
         <v>88</v>
@@ -32422,7 +32422,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>56.24%</t>
+          <t>55.85%</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -32454,7 +32454,7 @@
         </is>
       </c>
       <c r="L364" t="n">
-        <v>5951.78</v>
+        <v>5936.92</v>
       </c>
       <c r="M364" t="n">
         <v>100</v>
@@ -32541,7 +32541,7 @@
         </is>
       </c>
       <c r="L365" t="n">
-        <v>6199.77</v>
+        <v>6184.29</v>
       </c>
       <c r="M365" t="n">
         <v>0</v>
@@ -32632,7 +32632,7 @@
         </is>
       </c>
       <c r="L366" t="n">
-        <v>11903.56</v>
+        <v>11873.84</v>
       </c>
       <c r="M366" t="n">
         <v>88</v>
@@ -32905,7 +32905,7 @@
         </is>
       </c>
       <c r="L369" t="n">
-        <v>7439.73</v>
+        <v>7421.15</v>
       </c>
       <c r="M369" t="n">
         <v>0</v>
@@ -32964,7 +32964,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>-35.55%</t>
+          <t>-35.71%</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -32996,7 +32996,7 @@
         </is>
       </c>
       <c r="L370" t="n">
-        <v>6943.75</v>
+        <v>6926.41</v>
       </c>
       <c r="M370" t="n">
         <v>88</v>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -33219,7 +33219,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -33393,7 +33393,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -33480,7 +33480,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -33654,7 +33654,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -33741,7 +33741,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -34495,7 +34495,7 @@
         </is>
       </c>
       <c r="L387" t="n">
-        <v>3967.85</v>
+        <v>3957.95</v>
       </c>
       <c r="M387" t="n">
         <v>88</v>
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="L391" t="n">
-        <v>9671.65</v>
+        <v>9647.5</v>
       </c>
       <c r="M391" t="n">
         <v>100</v>
@@ -34938,7 +34938,7 @@
         </is>
       </c>
       <c r="L392" t="n">
-        <v>8183.7</v>
+        <v>8163.27</v>
       </c>
       <c r="M392" t="n">
         <v>22</v>
@@ -35029,7 +35029,7 @@
         </is>
       </c>
       <c r="L393" t="n">
-        <v>5827.79</v>
+        <v>5813.24</v>
       </c>
       <c r="M393" t="n">
         <v>88</v>
@@ -35266,7 +35266,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>68.17%</t>
+          <t>67.75%</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -35298,7 +35298,7 @@
         </is>
       </c>
       <c r="L396" t="n">
-        <v>1859.93</v>
+        <v>1855.29</v>
       </c>
       <c r="M396" t="n">
         <v>100</v>
@@ -35444,7 +35444,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>24.70%</t>
+          <t>24.39%</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -35476,7 +35476,7 @@
         </is>
       </c>
       <c r="L398" t="n">
-        <v>15474.63</v>
+        <v>15436</v>
       </c>
       <c r="M398" t="n">
         <v>100</v>
@@ -35563,7 +35563,7 @@
         </is>
       </c>
       <c r="L399" t="n">
-        <v>13267.51</v>
+        <v>13234.39</v>
       </c>
       <c r="M399" t="n">
         <v>100</v>
@@ -35705,7 +35705,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>64.83%</t>
+          <t>64.42%</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -35737,7 +35737,7 @@
         </is>
       </c>
       <c r="L401" t="n">
-        <v>9919.639999999999</v>
+        <v>9894.870000000001</v>
       </c>
       <c r="M401" t="n">
         <v>100</v>
@@ -35824,7 +35824,7 @@
         </is>
       </c>
       <c r="L402" t="n">
-        <v>14.88</v>
+        <v>14.84</v>
       </c>
       <c r="M402" t="n">
         <v>22</v>
@@ -35883,7 +35883,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -35915,7 +35915,7 @@
         </is>
       </c>
       <c r="L403" t="n">
-        <v>1611.94</v>
+        <v>1607.92</v>
       </c>
       <c r="M403" t="n">
         <v>100</v>
@@ -36002,7 +36002,7 @@
         </is>
       </c>
       <c r="L404" t="n">
-        <v>3344.16</v>
+        <v>3335.81</v>
       </c>
       <c r="M404" t="n">
         <v>22</v>
@@ -36184,7 +36184,7 @@
         </is>
       </c>
       <c r="L406" t="n">
-        <v>3298.03</v>
+        <v>3289.8</v>
       </c>
       <c r="M406" t="n">
         <v>22</v>
@@ -36334,7 +36334,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>-13.71%</t>
+          <t>-13.93%</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -36366,7 +36366,7 @@
         </is>
       </c>
       <c r="L408" t="n">
-        <v>2336.24</v>
+        <v>2330.41</v>
       </c>
       <c r="M408" t="n">
         <v>100</v>
@@ -36453,7 +36453,7 @@
         </is>
       </c>
       <c r="L409" t="n">
-        <v>322.39</v>
+        <v>321.58</v>
       </c>
       <c r="M409" t="n">
         <v>22</v>
@@ -36805,7 +36805,7 @@
         </is>
       </c>
       <c r="L413" t="n">
-        <v>15139.84</v>
+        <v>15102.04</v>
       </c>
       <c r="M413" t="n">
         <v>22</v>
@@ -36941,7 +36941,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -37560,7 +37560,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>-17.27%</t>
+          <t>-17.48%</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -37592,7 +37592,7 @@
         </is>
       </c>
       <c r="L422" t="n">
-        <v>1611.94</v>
+        <v>1607.92</v>
       </c>
       <c r="M422" t="n">
         <v>100</v>
@@ -37734,7 +37734,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>-52.33%</t>
+          <t>-52.44%</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -37766,7 +37766,7 @@
         </is>
       </c>
       <c r="L424" t="n">
-        <v>21.45</v>
+        <v>21.4</v>
       </c>
       <c r="M424" t="n">
         <v>100</v>
@@ -37853,7 +37853,7 @@
         </is>
       </c>
       <c r="L425" t="n">
-        <v>3223.88</v>
+        <v>3215.83</v>
       </c>
       <c r="M425" t="n">
         <v>100</v>
@@ -38205,7 +38205,7 @@
         </is>
       </c>
       <c r="L429" t="n">
-        <v>426.67</v>
+        <v>425.6</v>
       </c>
       <c r="M429" t="n">
         <v>0</v>
@@ -38355,7 +38355,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>115.72%</t>
+          <t>115.18%</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -38387,7 +38387,7 @@
         </is>
       </c>
       <c r="L431" t="n">
-        <v>22319.18</v>
+        <v>22263.46</v>
       </c>
       <c r="M431" t="n">
         <v>22</v>
@@ -38436,7 +38436,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -38478,7 +38478,7 @@
         </is>
       </c>
       <c r="L432" t="n">
-        <v>6943.75</v>
+        <v>6926.41</v>
       </c>
       <c r="M432" t="n">
         <v>22</v>
@@ -38537,7 +38537,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>476.58%</t>
+          <t>475.14%</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -38569,7 +38569,7 @@
         </is>
       </c>
       <c r="L433" t="n">
-        <v>5765.79</v>
+        <v>5751.39</v>
       </c>
       <c r="M433" t="n">
         <v>100</v>
@@ -38614,7 +38614,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -38747,7 +38747,7 @@
         </is>
       </c>
       <c r="L435" t="n">
-        <v>3099.89</v>
+        <v>3092.15</v>
       </c>
       <c r="M435" t="n">
         <v>88</v>
@@ -39020,7 +39020,7 @@
         </is>
       </c>
       <c r="L438" t="n">
-        <v>2727.9</v>
+        <v>2721.09</v>
       </c>
       <c r="M438" t="n">
         <v>88</v>
@@ -39069,7 +39069,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -39253,7 +39253,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>4.57%</t>
+          <t>4.31%</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -39285,7 +39285,7 @@
         </is>
       </c>
       <c r="L441" t="n">
-        <v>2479.91</v>
+        <v>2473.72</v>
       </c>
       <c r="M441" t="n">
         <v>100</v>
@@ -39340,7 +39340,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>63.69%</t>
+          <t>63.28%</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -39372,7 +39372,7 @@
         </is>
       </c>
       <c r="L442" t="n">
-        <v>3719.86</v>
+        <v>3710.58</v>
       </c>
       <c r="M442" t="n">
         <v>100</v>
@@ -39546,7 +39546,7 @@
         </is>
       </c>
       <c r="L444" t="n">
-        <v>2107.92</v>
+        <v>2102.66</v>
       </c>
       <c r="M444" t="n">
         <v>100</v>
@@ -39601,7 +39601,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -39633,7 +39633,7 @@
         </is>
       </c>
       <c r="L445" t="n">
-        <v>2107.92</v>
+        <v>2102.66</v>
       </c>
       <c r="M445" t="n">
         <v>100</v>
@@ -39720,7 +39720,7 @@
         </is>
       </c>
       <c r="L446" t="n">
-        <v>2709.1</v>
+        <v>2702.34</v>
       </c>
       <c r="M446" t="n">
         <v>0</v>
@@ -40131,7 +40131,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>35.27%</t>
+          <t>34.91%</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -40163,7 +40163,7 @@
         </is>
       </c>
       <c r="L451" t="n">
-        <v>14.88</v>
+        <v>14.84</v>
       </c>
       <c r="M451" t="n">
         <v>100</v>
@@ -40218,7 +40218,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>130.57%</t>
+          <t>130.00%</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -40250,7 +40250,7 @@
         </is>
       </c>
       <c r="L452" t="n">
-        <v>16.14</v>
+        <v>16.1</v>
       </c>
       <c r="M452" t="n">
         <v>100</v>
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="L454" t="n">
-        <v>5765.79</v>
+        <v>5751.39</v>
       </c>
       <c r="M454" t="n">
         <v>100</v>
@@ -40511,7 +40511,7 @@
         </is>
       </c>
       <c r="L455" t="n">
-        <v>3967.85</v>
+        <v>3957.95</v>
       </c>
       <c r="M455" t="n">
         <v>88</v>
@@ -40602,7 +40602,7 @@
         </is>
       </c>
       <c r="L456" t="n">
-        <v>458.78</v>
+        <v>457.64</v>
       </c>
       <c r="M456" t="n">
         <v>0</v>
@@ -40780,7 +40780,7 @@
         </is>
       </c>
       <c r="L458" t="n">
-        <v>9919.639999999999</v>
+        <v>9894.870000000001</v>
       </c>
       <c r="M458" t="n">
         <v>88</v>
@@ -40958,7 +40958,7 @@
         </is>
       </c>
       <c r="L460" t="n">
-        <v>14383.47</v>
+        <v>14347.56</v>
       </c>
       <c r="M460" t="n">
         <v>88</v>
@@ -41007,7 +41007,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>María Paz Galleguillos</t>
+          <t>Jorge Pablo Caro</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -41104,7 +41104,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>28.10%</t>
+          <t>27.78%</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -41136,7 +41136,7 @@
         </is>
       </c>
       <c r="L462" t="n">
-        <v>2107.92</v>
+        <v>2102.66</v>
       </c>
       <c r="M462" t="n">
         <v>100</v>
@@ -41163,6 +41163,93 @@
         </is>
       </c>
       <c r="S462" t="inlineStr">
+        <is>
+          <t>robusta</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>mrigoli@fidelis.cl</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Raquel Cheneaux Valz</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Ruta Inteligencia Comunal</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>pdf_missing</t>
+        </is>
+      </c>
+      <c r="H463" t="n">
+        <v>65</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Sin tasación referencial</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Enviar Inteligencia Comunal (Fallback)</t>
+        </is>
+      </c>
+      <c r="L463" t="n">
+        <v>130</v>
+      </c>
+      <c r="M463" t="n">
+        <v>100</v>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr"/>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
         <is>
           <t>robusta</t>
         </is>
